--- a/results/reliability_eval/Llama-3-8B_P103_sample_15_tokens_0.1_temp_first_thought_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P103_sample_15_tokens_0.1_temp_first_thought_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.4263230855406587</v>
+        <v>0.4506838849135361</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4062542150075856</v>
+        <v>0.6662841050851767</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4263230855406587</v>
+        <v>0.4506838849135361</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4062542150075856</v>
+        <v>0.6662841050851767</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5692924872355944</v>
+        <v>0.5317391547406083</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4689160612236403</v>
+        <v>0.7197141152604472</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9960890747972</v>
+        <v>0.98412343470483</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9943807851067843</v>
+        <v>0.9914904208057377</v>
       </c>
       <c r="I2" t="n">
-        <v>0.457</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
   </sheetData>
